--- a/artfynd/A 8231-2020 artfynd.xlsx
+++ b/artfynd/A 8231-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 8231-2020 artfynd.xlsx
+++ b/artfynd/A 8231-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2268,10 +2268,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>82985905</v>
+        <v>82985613</v>
       </c>
       <c r="B15" t="n">
-        <v>95511</v>
+        <v>93375</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2284,21 +2284,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221944</v>
+        <v>2180</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2385,10 +2385,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>82985613</v>
+        <v>82985633</v>
       </c>
       <c r="B16" t="n">
-        <v>93375</v>
+        <v>98520</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2401,21 +2401,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2180</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2502,10 +2502,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>82985633</v>
+        <v>82985664</v>
       </c>
       <c r="B17" t="n">
-        <v>98520</v>
+        <v>101680</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2518,21 +2518,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2619,10 +2619,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>82985664</v>
+        <v>82985670</v>
       </c>
       <c r="B18" t="n">
-        <v>101680</v>
+        <v>8377</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2635,27 +2635,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222412</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2736,10 +2737,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>82985670</v>
+        <v>83897594</v>
       </c>
       <c r="B19" t="n">
-        <v>8377</v>
+        <v>101680</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2752,39 +2753,38 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>222412</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skog vid Pauliströmsån, Venshult, Sm</t>
+          <t>Järnforsen, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>534371.669517467</v>
+        <v>534219.0494881091</v>
       </c>
       <c r="R19" t="n">
-        <v>6365008.30037332</v>
+        <v>6365130.854101896</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2020-03-21</t>
+          <t>2020-03-26</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2020-03-21</t>
+          <t>2020-03-26</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -2842,22 +2842,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>83897594</v>
+        <v>83897597</v>
       </c>
       <c r="B20" t="n">
-        <v>101680</v>
+        <v>98520</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2870,21 +2870,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2971,10 +2971,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>83897597</v>
+        <v>83897494</v>
       </c>
       <c r="B21" t="n">
-        <v>98520</v>
+        <v>103265</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2987,21 +2987,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>534219.0494881091</v>
+        <v>534477.8479081134</v>
       </c>
       <c r="R21" t="n">
-        <v>6365130.854101896</v>
+        <v>6365019.964124883</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3088,10 +3088,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>83897494</v>
+        <v>83897611</v>
       </c>
       <c r="B22" t="n">
-        <v>103265</v>
+        <v>95519</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3104,21 +3104,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3132,10 +3132,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>534477.8479081134</v>
+        <v>534210.2653518117</v>
       </c>
       <c r="R22" t="n">
-        <v>6365019.964124883</v>
+        <v>6365149.086320915</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3205,10 +3205,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>83897611</v>
+        <v>83993534</v>
       </c>
       <c r="B23" t="n">
-        <v>95519</v>
+        <v>4711</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3221,27 +3221,28 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>100299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3249,10 +3250,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>534210.2653518117</v>
+        <v>534273.0488381537</v>
       </c>
       <c r="R23" t="n">
-        <v>6365149.086320915</v>
+        <v>6365060.236563515</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3279,7 +3280,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2020-03-26</t>
+          <t>2020-03-30</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
@@ -3289,7 +3290,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2020-03-26</t>
+          <t>2020-03-30</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3322,10 +3323,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>83993534</v>
+        <v>83993456</v>
       </c>
       <c r="B24" t="n">
-        <v>4711</v>
+        <v>93235</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3338,28 +3339,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100299</v>
+        <v>210</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3367,10 +3371,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>534273.0488381537</v>
+        <v>534503.7590702465</v>
       </c>
       <c r="R24" t="n">
-        <v>6365060.236563515</v>
+        <v>6365018.029326913</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3413,6 +3417,11 @@
       <c r="AB24" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>7 stänglar på grov låga</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3440,10 +3449,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>83993456</v>
+        <v>83993298</v>
       </c>
       <c r="B25" t="n">
-        <v>93235</v>
+        <v>98520</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3456,28 +3465,24 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
@@ -3488,10 +3493,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>534503.7590702465</v>
+        <v>534555.0420364931</v>
       </c>
       <c r="R25" t="n">
-        <v>6365018.029326913</v>
+        <v>6365014.155654991</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3534,11 +3539,6 @@
       <c r="AB25" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>7 stänglar på grov låga</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3566,10 +3566,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>83993298</v>
+        <v>83993479</v>
       </c>
       <c r="B26" t="n">
-        <v>98520</v>
+        <v>101680</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3582,21 +3582,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3610,10 +3610,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>534555.0420364931</v>
+        <v>534245.0501227465</v>
       </c>
       <c r="R26" t="n">
-        <v>6365014.155654991</v>
+        <v>6365118.150297746</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3683,10 +3683,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>83993479</v>
+        <v>87913347</v>
       </c>
       <c r="B27" t="n">
-        <v>101680</v>
+        <v>90653</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3699,38 +3699,45 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222412</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Järnforsen, Sm</t>
+          <t>Pauliströmsån, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>534245.0501227465</v>
+        <v>534222.1076248427</v>
       </c>
       <c r="R27" t="n">
-        <v>6365118.150297746</v>
+        <v>6365087.80685693</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3757,7 +3764,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2020-03-30</t>
+          <t>2020-09-06</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
@@ -3767,7 +3774,7 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2020-03-30</t>
+          <t>2020-09-06</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -3788,22 +3795,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Hildingsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Hildingsson, Johan Staaf, Janne Kolehmainen, Pontus Axén</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>87913347</v>
+        <v>97362963</v>
       </c>
       <c r="B28" t="n">
-        <v>90653</v>
+        <v>89608</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3812,25 +3819,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>1101</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3847,17 +3854,17 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Pauliströmsån, Sm</t>
+          <t>Pauliströmsån (sydväst Stjärneberg), Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>534222.1076248427</v>
+        <v>534256.5948540401</v>
       </c>
       <c r="R28" t="n">
-        <v>6365087.80685693</v>
+        <v>6365092.403394971</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3881,7 +3888,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2020-09-06</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
@@ -3891,7 +3898,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2020-09-06</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -3912,22 +3919,26 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Hildingsson, Johan Staaf, Janne Kolehmainen, Pontus Axén</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>97362963</v>
+        <v>97362952</v>
       </c>
       <c r="B29" t="n">
-        <v>89608</v>
+        <v>85177</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3936,35 +3947,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1101</v>
+        <v>445</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -3975,10 +3986,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>534256.5948540401</v>
+        <v>534209.5113182438</v>
       </c>
       <c r="R29" t="n">
-        <v>6365092.403394971</v>
+        <v>6365110.314606668</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4052,10 +4063,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>97362952</v>
+        <v>97362957</v>
       </c>
       <c r="B30" t="n">
-        <v>85177</v>
+        <v>90674</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4064,35 +4075,35 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>445</v>
+        <v>5964</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -4103,10 +4114,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>534209.5113182438</v>
+        <v>534215.3773098157</v>
       </c>
       <c r="R30" t="n">
-        <v>6365110.314606668</v>
+        <v>6365118.4399184</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4180,10 +4191,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>97362957</v>
+        <v>97362966</v>
       </c>
       <c r="B31" t="n">
-        <v>90674</v>
+        <v>90661</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4192,35 +4203,35 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5964</v>
+        <v>2058</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -4231,10 +4242,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>534215.3773098157</v>
+        <v>534278.8153302373</v>
       </c>
       <c r="R31" t="n">
-        <v>6365118.4399184</v>
+        <v>6365080.206377684</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4301,134 +4312,6 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>97362966</v>
-      </c>
-      <c r="B32" t="n">
-        <v>90661</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>2058</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Koppartaggsvamp</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Hydnellum lundellii</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Pauliströmsån (sydväst Stjärneberg), Sm</t>
-        </is>
-      </c>
-      <c r="Q32" t="n">
-        <v>534278.8153302373</v>
-      </c>
-      <c r="R32" t="n">
-        <v>6365080.206377684</v>
-      </c>
-      <c r="S32" t="n">
-        <v>10</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Hultsfred</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>Järeda</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2021-09-15</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>2021-09-15</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF32" t="inlineStr"/>
-      <c r="AG32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>Tobias Ivarsson</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>Tobias Ivarsson</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
         <is>
           <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
